--- a/backend/income_details.xlsx
+++ b/backend/income_details.xlsx
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,44 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Source</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Amount</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Bussiness</v>
-      </c>
-      <c r="B2">
-        <v>1000</v>
-      </c>
-      <c r="C2" s="1">
-        <v>45843.22928240741</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="B3">
-        <v>6000</v>
-      </c>
-      <c r="C3" s="1">
-        <v>45840.79550543981</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/income_details.xlsx
+++ b/backend/income_details.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -413,32 +413,32 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bug Fixed</v>
+        <v>Cashback</v>
       </c>
       <c r="B2">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="C2" s="1">
-        <v>45844.22928240741</v>
+        <v>45847.22928240741</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Bussiness</v>
+        <v>Bug Fixed</v>
       </c>
       <c r="B3">
-        <v>1000</v>
+        <v>10000</v>
       </c>
       <c r="C3" s="1">
-        <v>45843.22928240741</v>
+        <v>45844.22928240741</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Apps</v>
+        <v>Bussiness</v>
       </c>
       <c r="B4">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="C4" s="1">
         <v>45843.22928240741</v>
@@ -446,18 +446,29 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>Apps</v>
+      </c>
+      <c r="B5">
+        <v>500</v>
+      </c>
+      <c r="C5" s="1">
+        <v>45843.22928240741</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
         <v>Salary</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>6000</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C6" s="1">
         <v>45840.79550543981</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>